--- a/reports/Lich_Truc_Toi_Uu_Hung_Vuong_Concert.xlsx
+++ b/reports/Lich_Truc_Toi_Uu_Hung_Vuong_Concert.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="515">
   <si>
     <t>HÙNG VƯƠNG CONCERT - PROJECT F&amp;B | TỔNG HỢP TOÀN BỘ LỊCH TRỰC TUẦN</t>
   </si>
@@ -69,7 +69,7 @@
     <t>24/08/2026</t>
   </si>
   <si>
-    <t>7h - 9h</t>
+    <t>07h00 - 09h30</t>
   </si>
   <si>
     <t>3 Chính + 1 DP</t>
@@ -78,7 +78,7 @@
     <t>Lý Minh Khang</t>
   </si>
   <si>
-    <t xml:space="preserve">[Chính]: Lý Minh Khang (Ban), Hồ Thị Mai (Ban), Huỳnh Minh Nam (Ban)
+    <t xml:space="preserve">[Chính]: Lý Minh Khang (Ban), Hoàng Quốc Em (Ban), Huỳnh Minh Nam (Ban)
 [DP]: Huỳnh Thảo Phương (Ban)</t>
   </si>
   <si>
@@ -88,7 +88,7 @@
     <t>CA002</t>
   </si>
   <si>
-    <t>9h - 11h</t>
+    <t>09h35 - 12h00</t>
   </si>
   <si>
     <t>Hoàng Minh Hương</t>
@@ -101,7 +101,7 @@
     <t>CA003</t>
   </si>
   <si>
-    <t>11h - 13h</t>
+    <t>12h05 - 14h00</t>
   </si>
   <si>
     <t>Lý Ngọc Khang</t>
@@ -114,26 +114,26 @@
     <t>CA004</t>
   </si>
   <si>
-    <t>13h - 15h</t>
+    <t>14h05 - 16h05</t>
   </si>
   <si>
     <t>Đỗ Hồng Uyên</t>
   </si>
   <si>
     <t xml:space="preserve">[Chính]: Đỗ Hồng Uyên (Ban), Huỳnh Minh Nam (Ban), Trần Đức Khang (Ban)
-[DP]: Trần Tuấn Châu (Ban)</t>
+[DP]: Hồ Nhật Uyên (Ban)</t>
   </si>
   <si>
     <t>CA005</t>
   </si>
   <si>
-    <t>15h - 17h</t>
-  </si>
-  <si>
-    <t>Bùi Gia Trang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Chính]: Bùi Gia Trang (Ban), Đỗ Hồng Uyên (Ban), Lê Hải Yến (Ban)
+    <t>16h10 - 18h00</t>
+  </si>
+  <si>
+    <t>Đặng Bảo Quyên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Chính]: Đặng Bảo Quyên (Ban), Đỗ Hồng Uyên (Ban), Lê Hải Yến (Ban)
 [DP]: Võ Tuấn Châu (Ban)</t>
   </si>
   <si>
@@ -176,7 +176,7 @@
     <t>Đỗ Thị Bình</t>
   </si>
   <si>
-    <t xml:space="preserve">[Chính]: Hồ Nhật Uyên (Ban), Đỗ Thị Bình (Ban), Trần Hoàng Bình (Ban)
+    <t xml:space="preserve">[Chính]: Hồ Nhật Uyên (Ban), Đặng Quốc Dung (Ban), Đỗ Thị Bình (Ban)
 [DP]: Võ Tuấn Châu (Ban)</t>
   </si>
   <si>
@@ -186,8 +186,8 @@
     <t>Dương Ngọc Nam</t>
   </si>
   <si>
-    <t xml:space="preserve">[Chính]: Võ Bảo Sơn (Ban), Dương Ngọc Nam (Ban), Đỗ Thị Giang (Ban)
-[DP]: Lý Tuấn Hà (Ban)</t>
+    <t xml:space="preserve">[Chính]: Võ Bảo Sơn (Ban), Dương Ngọc Nam (Ban), Trần Hoàng Bình (Ban)
+[DP]: Lê Nhật Quyên (Ban)</t>
   </si>
   <si>
     <t>CA011</t>
@@ -199,10 +199,7 @@
     <t>26/08/2026</t>
   </si>
   <si>
-    <t>Lê Gia Khang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Chính]: Hồ Thị Mai (Ban), Huỳnh Minh Nam (Ban), Lê Gia Khang (Ban)
+    <t xml:space="preserve">[Chính]: Hồ Thị Mai (Ban), Huỳnh Minh Nam (Ban), Huỳnh Quốc Khang (Ban)
 [DP]: Trần Hoàng Bình (Ban)</t>
   </si>
   <si>
@@ -222,8 +219,8 @@
     <t>Đỗ Thị Anh</t>
   </si>
   <si>
-    <t xml:space="preserve">[Chính]: Võ Bảo Sơn (Ban), Đỗ Thị Anh (Ban), Lý Tuấn Hà (Ban)
-[DP]: Phạm Minh Yến (Ban)</t>
+    <t xml:space="preserve">[Chính]: Võ Bảo Sơn (Ban), Hồ Minh Quyên (Ban), Đỗ Thị Anh (Ban)
+[DP]: Lý Tuấn Hà (Ban)</t>
   </si>
   <si>
     <t>CA014</t>
@@ -236,11 +233,11 @@
     <t>CA015</t>
   </si>
   <si>
-    <t>Dương Minh Sơn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Chính]: Dương Minh Sơn (Ban), Huỳnh Thị Uyên (Ban), Lê Gia Khang (Ban)
-[DP]: Huỳnh Hải Sơn (Ban)</t>
+    <t>Huỳnh Thị Uyên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Chính]: Huỳnh Thị Uyên (Ban), Lê Gia Khang (Ban), Nguyễn Minh Linh (Ban)
+[DP]: Trần Đức Khang (Ban)</t>
   </si>
   <si>
     <t>CA016</t>
@@ -255,7 +252,7 @@
     <t>Hồ Hải Linh</t>
   </si>
   <si>
-    <t xml:space="preserve">[Chính]: Lê Nhật Quyên (Ban), Hồ Hải Linh (Ban), Lý Tuấn Hà (Ban)
+    <t xml:space="preserve">[Chính]: Hồ Hải Linh (Ban), Lý Tuấn Hà (Ban), Võ Thị Dung (Ban)
 [DP]: Vũ Minh Linh (Ban)</t>
   </si>
   <si>
@@ -273,10 +270,13 @@
   </si>
   <si>
     <t xml:space="preserve">[Chính]: Đỗ Tuấn Uyên (Ban), Nguyễn Gia Nam (Ban), Đặng Bảo Quyên (Ban)
-[DP]: Hoàng Quốc Em (Ban)</t>
+[DP]: Đỗ Hồng Uyên (Ban)</t>
   </si>
   <si>
     <t>CA019</t>
+  </si>
+  <si>
+    <t>Dương Minh Sơn</t>
   </si>
   <si>
     <t xml:space="preserve">[Chính]: Dương Minh Sơn (Ban), Huỳnh Hải Sơn (Ban), Phạm Minh Yến (Ban)
@@ -299,7 +299,7 @@
     <t>28/08/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">[Chính]: Lý Ngọc Khang (Ban), Hồ Ngọc Bình (Ban), Lê Hải Yến (Ban)
+    <t xml:space="preserve">[Chính]: Lý Ngọc Khang (Ban), Lê Hải Yến (Ban), Lê Nhật Quyên (Ban)
 [DP]: Nguyễn Minh Linh (Ban)</t>
   </si>
   <si>
@@ -309,21 +309,18 @@
     <t>Lý Thảo Hà</t>
   </si>
   <si>
-    <t xml:space="preserve">[Chính]: Dương Quốc Châu (Ban), Bùi Gia Trang (Ban), Lý Thảo Hà (Ban)
-[DP]: Hồ Quốc Châu (Ban)</t>
+    <t xml:space="preserve">[Chính]: Bùi Gia Trang (Ban), Lý Thảo Hà (Ban), Phạm Hồng Sơn (Ban)
+[DP]: Phạm Minh Yến (Ban)</t>
   </si>
   <si>
     <t>CA023</t>
   </si>
   <si>
-    <t xml:space="preserve">[Chính]: Dương Minh Sơn (Ban), Đặng Quốc Dung (Ban), Hồ Ngọc Bình (Ban)
-[DP]: Võ Thị Dung (Ban)</t>
+    <t xml:space="preserve">[Chính]: Dương Minh Sơn (Ban), Đặng Quốc Dung (Ban), Đỗ Thị Giang (Ban)
+[DP]: Võ Nhật Vinh (Ban)</t>
   </si>
   <si>
     <t>CA024</t>
-  </si>
-  <si>
-    <t>Huỳnh Thị Uyên</t>
   </si>
   <si>
     <t xml:space="preserve">[Chính]: Huỳnh Thảo Phương (Ban), Huỳnh Thị Uyên (Ban), Trần Tuấn Châu (Ban)
@@ -333,7 +330,7 @@
     <t>CA025</t>
   </si>
   <si>
-    <t xml:space="preserve">[Chính]: Đỗ Thị Bình (Ban), Vũ Minh Linh (Ban), Dương Tuấn Quyên (Ban)
+    <t xml:space="preserve">[Chính]: Dương Quốc Châu (Ban), Đỗ Thị Bình (Ban), Vũ Minh Linh (Ban)
 [DP]: Đỗ Thị Anh (Ban)</t>
   </si>
   <si>
@@ -349,8 +346,8 @@
     <t>Hồ Hồng Uyên</t>
   </si>
   <si>
-    <t xml:space="preserve">[Chính]: Đỗ Tuấn Uyên (Ban), Đỗ Hồng Uyên (Ban), Hồ Hồng Uyên (Ban)
-[DP]: Nguyễn Minh Linh (Ban)</t>
+    <t xml:space="preserve">[Chính]: Đỗ Tuấn Uyên (Ban), Đặng Quốc Dung (Ban), Hồ Hồng Uyên (Ban)
+[DP]: Hoàng Minh Hương (Ban)</t>
   </si>
   <si>
     <t>CA027</t>
@@ -370,11 +367,11 @@
     <t>CA029</t>
   </si>
   <si>
-    <t>Phạm Hồng Sơn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Chính]: Dương Quốc Châu (Ban), Lê Hải Yến (Ban), Phạm Hồng Sơn (Ban)
-[DP]: Võ Thị Dung (Ban)</t>
+    <t>Lê Gia Khang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Chính]: Dương Quốc Châu (Ban), Đỗ Thị Giang (Ban), Lê Gia Khang (Ban)
+[DP]: Lê Hải Yến (Ban)</t>
   </si>
   <si>
     <t>CA030</t>
@@ -383,8 +380,8 @@
     <t>Hồ Ngọc Bình</t>
   </si>
   <si>
-    <t xml:space="preserve">[Chính]: Hồ Minh Quyên (Ban), Hồ Ngọc Bình (Ban), Lê Quốc Mai (Ban)
-[DP]: Phạm Hồng Sơn (Ban)</t>
+    <t xml:space="preserve">[Chính]: Hồ Minh Quyên (Ban), Hồ Ngọc Bình (Ban), Phạm Hồng Sơn (Ban)
+[DP]: Trần Tuấn Châu (Ban)</t>
   </si>
   <si>
     <t>CA031</t>
@@ -396,15 +393,15 @@
     <t>30/08/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">[Chính]: Đỗ Thị Giang (Ban), Lý Thảo Hà (Ban), Trần Đức Khang (Ban)
-[DP]: Trần Đức Quyên (Ban)</t>
+    <t xml:space="preserve">[Chính]: Dương Tuấn Quyên (Ban), Đỗ Thị Giang (Ban), Lý Thảo Hà (Ban)
+[DP]: Trần Đức Khang (Ban)</t>
   </si>
   <si>
     <t>CA032</t>
   </si>
   <si>
-    <t xml:space="preserve">[Chính]: Dương Tuấn Quyên (Ban), Võ Thị Dung (Ban), Lê Nhật Quyên (Ban)
-[DP]: Huỳnh Minh Nam (Ban)</t>
+    <t xml:space="preserve">[Chính]: Dương Tuấn Quyên (Ban), Hoàng Quốc Em (Ban), Hồ Quốc Châu (Ban)
+[DP]: Huỳnh Hải Sơn (Ban)</t>
   </si>
   <si>
     <t>CA033</t>
@@ -413,8 +410,8 @@
     <t>Lê Quốc Mai</t>
   </si>
   <si>
-    <t xml:space="preserve">[Chính]: Bùi Thảo Châu (Ban), Lê Quốc Mai (Ban), Phạm Hồng Sơn (Ban)
-[DP]: Hồ Nhật Uyên (Ban)</t>
+    <t xml:space="preserve">[Chính]: Bùi Thảo Châu (Ban), Lê Quốc Mai (Ban), Nguyễn Minh Mai (Ban)
+[DP]: Vũ Minh Linh (Ban)</t>
   </si>
   <si>
     <t>CA034</t>
@@ -427,45 +424,52 @@
     <t>CA035</t>
   </si>
   <si>
-    <t>Trần Đức Quyên</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Chính]: Trần Đức Quyên (Ban), Lý Ngọc Khang (Ban), Đặng Quốc Dung (Ban)
+    <t>Nguyễn Minh Khang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Chính]: Nguyễn Minh Khang (Ban), Hồ Hồng Uyên (Ban), Hồ Thị Mai (Ban)
+[DP]: Trần Đức Quyên (Ban)</t>
+  </si>
+  <si>
+    <t>NGOAI_01</t>
+  </si>
+  <si>
+    <t>Điểm bán ngoài</t>
+  </si>
+  <si>
+    <t>17:00 - 19:30</t>
+  </si>
+  <si>
+    <t>Quán Café A</t>
+  </si>
+  <si>
+    <t>2 Chính + 1 DP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Chính]: Hồ Minh Quyên (Ban), Hồ Ngọc Bình (Ban)
+[DP]: Trần Tuấn Châu (Ban)</t>
+  </si>
+  <si>
+    <t>NGOAI_02</t>
+  </si>
+  <si>
+    <t>17:30 - 20:00</t>
+  </si>
+  <si>
+    <t>Quán Café B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Chính]: Lê Quốc Mai (Ban), Phạm Hồng Sơn (Ban)
+[DP]: Phạm Minh Yến (Ban)</t>
+  </si>
+  <si>
+    <t>NGOAI_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Chính]: Nguyễn Minh Khang (Ban), Trần Đức Quyên (Ban)
 [DP]: Nguyễn Minh Mai (Ban)</t>
   </si>
   <si>
-    <t>NGOAI_01</t>
-  </si>
-  <si>
-    <t>Điểm bán ngoài</t>
-  </si>
-  <si>
-    <t>17:00 - 19:30</t>
-  </si>
-  <si>
-    <t>Quán Café A</t>
-  </si>
-  <si>
-    <t>2 Chính + 1 DP</t>
-  </si>
-  <si>
-    <t>Trần Tuấn Châu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Chính]: Trần Tuấn Châu (Ban), Đặng Bảo Quyên (Ban)
-[DP]: Phạm Minh Yến (Ban)</t>
-  </si>
-  <si>
-    <t>NGOAI_03</t>
-  </si>
-  <si>
-    <t>Quán Café B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Chính]: Bùi Gia Trang (Ban), Đỗ Thị Bình (Ban)
-[DP]: Võ Tuấn Châu (Ban)</t>
-  </si>
-  <si>
     <t>NGOAI_04</t>
   </si>
   <si>
@@ -475,11 +479,8 @@
     <t>Quán Café C</t>
   </si>
   <si>
-    <t>Nguyễn Minh Khang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Chính]: Nguyễn Minh Khang (Ban), Hồ Hồng Uyên (Ban)
-[DP]: Hồ Thị Mai (Ban)</t>
+    <t xml:space="preserve">[Chính]: Lý Ngọc Khang (Ban), Bùi Gia Trang (Ban)
+[DP]: Đỗ Thị Bình (Ban)</t>
   </si>
   <si>
     <t>LỊCH TRỰC PHÒNG THANH NIÊN (THPT CHUYÊN HÙNG VƯƠNG) - CA TRONG</t>
@@ -501,7 +502,7 @@
   </si>
   <si>
     <t xml:space="preserve">• [Trực chính]: Lý Minh Khang (Ban Nhân sự - SĐT: 0793534874)
-• [Trực chính]: Hồ Thị Mai (Ban Nội dung - SĐT: 0311116152)
+• [Trực chính]: Hoàng Quốc Em (Ban Tài chính - SĐT: 0362268388)
 • [Trực chính]: Huỳnh Minh Nam (Ban Tài chính - SĐT: 0829014767)
 • [Dự phòng]: Huỳnh Thảo Phương (Ban Truyền thông - SĐT: 0822196937)</t>
   </si>
@@ -524,10 +525,10 @@
     <t xml:space="preserve">• [Trực chính]: Đỗ Hồng Uyên (Ban Tài chính - SĐT: 0975496513)
 • [Trực chính]: Huỳnh Minh Nam (Ban Tài chính - SĐT: 0829014767)
 • [Trực chính]: Trần Đức Khang (Ban Tài chính - SĐT: 0357809134)
-• [Dự phòng]: Trần Tuấn Châu (Ban Nội dung - SĐT: 0894131869)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• [Trực chính]: Bùi Gia Trang (Ban Nội dung - SĐT: 0859782071)
+• [Dự phòng]: Hồ Nhật Uyên (Ban Truyền thông - SĐT: 0899468044)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• [Trực chính]: Đặng Bảo Quyên (Ban Tài chính - SĐT: 0317565512)
 • [Trực chính]: Đỗ Hồng Uyên (Ban Tài chính - SĐT: 0975496513)
 • [Trực chính]: Lê Hải Yến (Ban Nội dung - SĐT: 0936968164)
 • [Dự phòng]: Võ Tuấn Châu (Ban Hậu cần - SĐT: 0848963834)</t>
@@ -552,20 +553,20 @@
   </si>
   <si>
     <t xml:space="preserve">• [Trực chính]: Hồ Nhật Uyên (Ban Truyền thông - SĐT: 0899468044)
+• [Trực chính]: Đặng Quốc Dung (Ban Nội dung - SĐT: 0387277434)
 • [Trực chính]: Đỗ Thị Bình (Ban Nhân sự - SĐT: 0832719374)
-• [Trực chính]: Trần Hoàng Bình (Ban Tài chính - SĐT: 0338299737)
 • [Dự phòng]: Võ Tuấn Châu (Ban Hậu cần - SĐT: 0848963834)</t>
   </si>
   <si>
     <t xml:space="preserve">• [Trực chính]: Võ Bảo Sơn (Ban Nội dung - SĐT: 0334957885)
 • [Trực chính]: Dương Ngọc Nam (Ban Nhân sự - SĐT: 0994024455)
-• [Trực chính]: Đỗ Thị Giang (Ban Truyền thông - SĐT: 0967974034)
-• [Dự phòng]: Lý Tuấn Hà (Ban Tài chính - SĐT: 0346886239)</t>
+• [Trực chính]: Trần Hoàng Bình (Ban Tài chính - SĐT: 0338299737)
+• [Dự phòng]: Lê Nhật Quyên (Ban Truyền thông - SĐT: 0913267736)</t>
   </si>
   <si>
     <t xml:space="preserve">• [Trực chính]: Hồ Thị Mai (Ban Nội dung - SĐT: 0311116152)
 • [Trực chính]: Huỳnh Minh Nam (Ban Tài chính - SĐT: 0829014767)
-• [Trực chính]: Lê Gia Khang (Ban Nhân sự - SĐT: 0756981693)
+• [Trực chính]: Huỳnh Quốc Khang (Ban Sự kiện - SĐT: 0827648350)
 • [Dự phòng]: Trần Hoàng Bình (Ban Tài chính - SĐT: 0338299737)</t>
   </si>
   <si>
@@ -576,9 +577,9 @@
   </si>
   <si>
     <t xml:space="preserve">• [Trực chính]: Võ Bảo Sơn (Ban Nội dung - SĐT: 0334957885)
+• [Trực chính]: Hồ Minh Quyên (Ban Truyền thông - SĐT: 0916272046)
 • [Trực chính]: Đỗ Thị Anh (Ban Sự kiện - SĐT: 0981960013)
-• [Trực chính]: Lý Tuấn Hà (Ban Tài chính - SĐT: 0346886239)
-• [Dự phòng]: Phạm Minh Yến (Ban Truyền thông - SĐT: 0379979955)</t>
+• [Dự phòng]: Lý Tuấn Hà (Ban Tài chính - SĐT: 0346886239)</t>
   </si>
   <si>
     <t xml:space="preserve">• [Trực chính]: Lý Minh Khang (Ban Nhân sự - SĐT: 0793534874)
@@ -587,15 +588,15 @@
 • [Dự phòng]: Hồ Quốc Châu (Ban Nội dung - SĐT: 0303669096)</t>
   </si>
   <si>
-    <t xml:space="preserve">• [Trực chính]: Dương Minh Sơn (Ban Sự kiện - SĐT: 0373782639)
-• [Trực chính]: Huỳnh Thị Uyên (Ban Sự kiện - SĐT: 0851925462)
+    <t xml:space="preserve">• [Trực chính]: Huỳnh Thị Uyên (Ban Sự kiện - SĐT: 0851925462)
 • [Trực chính]: Lê Gia Khang (Ban Nhân sự - SĐT: 0756981693)
-• [Dự phòng]: Huỳnh Hải Sơn (Ban Truyền thông - SĐT: 0718880592)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• [Trực chính]: Lê Nhật Quyên (Ban Truyền thông - SĐT: 0913267736)
-• [Trực chính]: Hồ Hải Linh (Ban Sự kiện - SĐT: 0351850671)
+• [Trực chính]: Nguyễn Minh Linh (Ban Hậu cần - SĐT: 0974648877)
+• [Dự phòng]: Trần Đức Khang (Ban Tài chính - SĐT: 0357809134)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• [Trực chính]: Hồ Hải Linh (Ban Sự kiện - SĐT: 0351850671)
 • [Trực chính]: Lý Tuấn Hà (Ban Tài chính - SĐT: 0346886239)
+• [Trực chính]: Võ Thị Dung (Ban Truyền thông - SĐT: 0358692617)
 • [Dự phòng]: Vũ Minh Linh (Ban Nội dung - SĐT: 0918384251)</t>
   </si>
   <si>
@@ -608,7 +609,7 @@
     <t xml:space="preserve">• [Trực chính]: Đỗ Tuấn Uyên (Ban Nội dung - SĐT: 0797703482)
 • [Trực chính]: Nguyễn Gia Nam (Ban Sự kiện - SĐT: 0323285884)
 • [Trực chính]: Đặng Bảo Quyên (Ban Tài chính - SĐT: 0317565512)
-• [Dự phòng]: Hoàng Quốc Em (Ban Tài chính - SĐT: 0362268388)</t>
+• [Dự phòng]: Đỗ Hồng Uyên (Ban Tài chính - SĐT: 0975496513)</t>
   </si>
   <si>
     <t xml:space="preserve">• [Trực chính]: Dương Minh Sơn (Ban Sự kiện - SĐT: 0373782639)
@@ -624,21 +625,21 @@
   </si>
   <si>
     <t xml:space="preserve">• [Trực chính]: Lý Ngọc Khang (Ban Sự kiện - SĐT: 0870482814)
-• [Trực chính]: Hồ Ngọc Bình (Ban Sự kiện - SĐT: 0388208121)
 • [Trực chính]: Lê Hải Yến (Ban Nội dung - SĐT: 0936968164)
+• [Trực chính]: Lê Nhật Quyên (Ban Truyền thông - SĐT: 0913267736)
 • [Dự phòng]: Nguyễn Minh Linh (Ban Hậu cần - SĐT: 0974648877)</t>
   </si>
   <si>
-    <t xml:space="preserve">• [Trực chính]: Dương Quốc Châu (Ban Tài chính - SĐT: 0350752735)
-• [Trực chính]: Bùi Gia Trang (Ban Nội dung - SĐT: 0859782071)
+    <t xml:space="preserve">• [Trực chính]: Bùi Gia Trang (Ban Nội dung - SĐT: 0859782071)
 • [Trực chính]: Lý Thảo Hà (Ban Sự kiện - SĐT: 0860576627)
-• [Dự phòng]: Hồ Quốc Châu (Ban Nội dung - SĐT: 0303669096)</t>
+• [Trực chính]: Phạm Hồng Sơn (Ban Nhân sự - SĐT: 0740640909)
+• [Dự phòng]: Phạm Minh Yến (Ban Truyền thông - SĐT: 0379979955)</t>
   </si>
   <si>
     <t xml:space="preserve">• [Trực chính]: Dương Minh Sơn (Ban Sự kiện - SĐT: 0373782639)
 • [Trực chính]: Đặng Quốc Dung (Ban Nội dung - SĐT: 0387277434)
-• [Trực chính]: Hồ Ngọc Bình (Ban Sự kiện - SĐT: 0388208121)
-• [Dự phòng]: Võ Thị Dung (Ban Truyền thông - SĐT: 0358692617)</t>
+• [Trực chính]: Đỗ Thị Giang (Ban Truyền thông - SĐT: 0967974034)
+• [Dự phòng]: Võ Nhật Vinh (Ban Hậu cần - SĐT: 0735240824)</t>
   </si>
   <si>
     <t xml:space="preserve">• [Trực chính]: Huỳnh Thảo Phương (Ban Truyền thông - SĐT: 0822196937)
@@ -647,16 +648,16 @@
 • [Dự phòng]: Lê Gia Khang (Ban Nhân sự - SĐT: 0756981693)</t>
   </si>
   <si>
-    <t xml:space="preserve">• [Trực chính]: Đỗ Thị Bình (Ban Nhân sự - SĐT: 0832719374)
+    <t xml:space="preserve">• [Trực chính]: Dương Quốc Châu (Ban Tài chính - SĐT: 0350752735)
+• [Trực chính]: Đỗ Thị Bình (Ban Nhân sự - SĐT: 0832719374)
 • [Trực chính]: Vũ Minh Linh (Ban Nội dung - SĐT: 0918384251)
-• [Trực chính]: Dương Tuấn Quyên (Ban Nhân sự - SĐT: 0732931839)
 • [Dự phòng]: Đỗ Thị Anh (Ban Sự kiện - SĐT: 0981960013)</t>
   </si>
   <si>
     <t xml:space="preserve">• [Trực chính]: Đỗ Tuấn Uyên (Ban Nội dung - SĐT: 0797703482)
-• [Trực chính]: Đỗ Hồng Uyên (Ban Tài chính - SĐT: 0975496513)
+• [Trực chính]: Đặng Quốc Dung (Ban Nội dung - SĐT: 0387277434)
 • [Trực chính]: Hồ Hồng Uyên (Ban Nhân sự - SĐT: 0959826204)
-• [Dự phòng]: Nguyễn Minh Linh (Ban Hậu cần - SĐT: 0974648877)</t>
+• [Dự phòng]: Hoàng Minh Hương (Ban Sự kiện - SĐT: 0396532871)</t>
   </si>
   <si>
     <t xml:space="preserve">• [Trực chính]: Hồ Nhật Uyên (Ban Truyền thông - SĐT: 0899468044)
@@ -672,33 +673,33 @@
   </si>
   <si>
     <t xml:space="preserve">• [Trực chính]: Dương Quốc Châu (Ban Tài chính - SĐT: 0350752735)
-• [Trực chính]: Lê Hải Yến (Ban Nội dung - SĐT: 0936968164)
-• [Trực chính]: Phạm Hồng Sơn (Ban Nhân sự - SĐT: 0740640909)
-• [Dự phòng]: Võ Thị Dung (Ban Truyền thông - SĐT: 0358692617)</t>
+• [Trực chính]: Đỗ Thị Giang (Ban Truyền thông - SĐT: 0967974034)
+• [Trực chính]: Lê Gia Khang (Ban Nhân sự - SĐT: 0756981693)
+• [Dự phòng]: Lê Hải Yến (Ban Nội dung - SĐT: 0936968164)</t>
   </si>
   <si>
     <t xml:space="preserve">• [Trực chính]: Hồ Minh Quyên (Ban Truyền thông - SĐT: 0916272046)
 • [Trực chính]: Hồ Ngọc Bình (Ban Sự kiện - SĐT: 0388208121)
-• [Trực chính]: Lê Quốc Mai (Ban Nhân sự - SĐT: 0794078161)
-• [Dự phòng]: Phạm Hồng Sơn (Ban Nhân sự - SĐT: 0740640909)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• [Trực chính]: Đỗ Thị Giang (Ban Truyền thông - SĐT: 0967974034)
+• [Trực chính]: Phạm Hồng Sơn (Ban Nhân sự - SĐT: 0740640909)
+• [Dự phòng]: Trần Tuấn Châu (Ban Nội dung - SĐT: 0894131869)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• [Trực chính]: Dương Tuấn Quyên (Ban Nhân sự - SĐT: 0732931839)
+• [Trực chính]: Đỗ Thị Giang (Ban Truyền thông - SĐT: 0967974034)
 • [Trực chính]: Lý Thảo Hà (Ban Sự kiện - SĐT: 0860576627)
-• [Trực chính]: Trần Đức Khang (Ban Tài chính - SĐT: 0357809134)
-• [Dự phòng]: Trần Đức Quyên (Ban Nhân sự - SĐT: 0849985698)</t>
+• [Dự phòng]: Trần Đức Khang (Ban Tài chính - SĐT: 0357809134)</t>
   </si>
   <si>
     <t xml:space="preserve">• [Trực chính]: Dương Tuấn Quyên (Ban Nhân sự - SĐT: 0732931839)
-• [Trực chính]: Võ Thị Dung (Ban Truyền thông - SĐT: 0358692617)
-• [Trực chính]: Lê Nhật Quyên (Ban Truyền thông - SĐT: 0913267736)
-• [Dự phòng]: Huỳnh Minh Nam (Ban Tài chính - SĐT: 0829014767)</t>
+• [Trực chính]: Hoàng Quốc Em (Ban Tài chính - SĐT: 0362268388)
+• [Trực chính]: Hồ Quốc Châu (Ban Nội dung - SĐT: 0303669096)
+• [Dự phòng]: Huỳnh Hải Sơn (Ban Truyền thông - SĐT: 0718880592)</t>
   </si>
   <si>
     <t xml:space="preserve">• [Trực chính]: Bùi Thảo Châu (Ban Truyền thông - SĐT: 0800379176)
 • [Trực chính]: Lê Quốc Mai (Ban Nhân sự - SĐT: 0794078161)
-• [Trực chính]: Phạm Hồng Sơn (Ban Nhân sự - SĐT: 0740640909)
-• [Dự phòng]: Hồ Nhật Uyên (Ban Truyền thông - SĐT: 0899468044)</t>
+• [Trực chính]: Nguyễn Minh Mai (Ban Nội dung - SĐT: 0960733754)
+• [Dự phòng]: Vũ Minh Linh (Ban Nội dung - SĐT: 0918384251)</t>
   </si>
   <si>
     <t xml:space="preserve">• [Trực chính]: Lê Nhật Quyên (Ban Truyền thông - SĐT: 0913267736)
@@ -707,10 +708,10 @@
 • [Dự phòng]: Hồ Hồng Uyên (Ban Nhân sự - SĐT: 0959826204)</t>
   </si>
   <si>
-    <t xml:space="preserve">• [Trực chính]: Trần Đức Quyên (Ban Nhân sự - SĐT: 0849985698)
-• [Trực chính]: Lý Ngọc Khang (Ban Sự kiện - SĐT: 0870482814)
-• [Trực chính]: Đặng Quốc Dung (Ban Nội dung - SĐT: 0387277434)
-• [Dự phòng]: Nguyễn Minh Mai (Ban Nội dung - SĐT: 0960733754)</t>
+    <t xml:space="preserve">• [Trực chính]: Nguyễn Minh Khang (Ban Nhân sự - SĐT: 0977589178)
+• [Trực chính]: Hồ Hồng Uyên (Ban Nhân sự - SĐT: 0959826204)
+• [Trực chính]: Hồ Thị Mai (Ban Nội dung - SĐT: 0311116152)
+• [Dự phòng]: Trần Đức Quyên (Ban Nhân sự - SĐT: 0849985698)</t>
   </si>
   <si>
     <t>LỊCH PHÂN BỔ NHÂN SỰ ĐIỂM BÁN NGOÀI - CA NGOÀI</t>
@@ -728,19 +729,24 @@
     <t>Danh Sách Nhân Sự (SĐT &amp; Phương Tiện)</t>
   </si>
   <si>
-    <t xml:space="preserve">• [Trực chính]: Trần Tuấn Châu - Ban Nội dung (SĐT: 0894131869) [Được đưa đón]
-• [Trực chính]: Đặng Bảo Quyên - Ban Tài chính (SĐT: 0317565512) [Tự đi xe máy]
+    <t xml:space="preserve">• [Trực chính]: Hồ Minh Quyên - Ban Truyền thông (SĐT: 0916272046) [Tự đi xe máy]
+• [Trực chính]: Hồ Ngọc Bình - Ban Sự kiện (SĐT: 0388208121) [Được đưa đón]
+• [Dự phòng]: Trần Tuấn Châu - Ban Nội dung (SĐT: 0894131869) [Được đưa đón]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• [Trực chính]: Lê Quốc Mai - Ban Nhân sự (SĐT: 0794078161) [Xe buýt]
+• [Trực chính]: Phạm Hồng Sơn - Ban Nhân sự (SĐT: 0740640909) [Xe buýt]
 • [Dự phòng]: Phạm Minh Yến - Ban Truyền thông (SĐT: 0379979955) [Được đưa đón]</t>
   </si>
   <si>
-    <t xml:space="preserve">• [Trực chính]: Bùi Gia Trang - Ban Nội dung (SĐT: 0859782071) [Tự đi xe máy]
-• [Trực chính]: Đỗ Thị Bình - Ban Nhân sự (SĐT: 0832719374) [Xe máy]
-• [Dự phòng]: Võ Tuấn Châu - Ban Hậu cần (SĐT: 0848963834) [Xe máy]</t>
-  </si>
-  <si>
     <t xml:space="preserve">• [Trực chính]: Nguyễn Minh Khang - Ban Nhân sự (SĐT: 0977589178) [Xe buýt]
-• [Trực chính]: Hồ Hồng Uyên - Ban Nhân sự (SĐT: 0959826204) [Được đưa đón]
-• [Dự phòng]: Hồ Thị Mai - Ban Nội dung (SĐT: 0311116152) [Xe đạp điện]</t>
+• [Trực chính]: Trần Đức Quyên - Ban Nhân sự (SĐT: 0849985698) [Xe đạp điện]
+• [Dự phòng]: Nguyễn Minh Mai - Ban Nội dung (SĐT: 0960733754) [Xe máy]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• [Trực chính]: Lý Ngọc Khang - Ban Sự kiện (SĐT: 0870482814) [Được đưa đón]
+• [Trực chính]: Bùi Gia Trang - Ban Nội dung (SĐT: 0859782071) [Tự đi xe máy]
+• [Dự phòng]: Đỗ Thị Bình - Ban Nhân sự (SĐT: 0832719374) [Xe máy]</t>
   </si>
   <si>
     <t>BÁO CÁO THỐNG KÊ &amp; PHÂN TÍCH HIỆU SUẤT NHÂN SỰ TRỰC CA</t>
@@ -818,7 +824,7 @@
     <t>0794078161</t>
   </si>
   <si>
-    <t>CA002, CA030, CA033</t>
+    <t>CA002, CA033, NGOAI_02</t>
   </si>
   <si>
     <t>TV003</t>
@@ -830,7 +836,7 @@
     <t>0827648350</t>
   </si>
   <si>
-    <t>CA007, CA008</t>
+    <t>CA007, CA008, CA011</t>
   </si>
   <si>
     <t>TV004</t>
@@ -845,7 +851,7 @@
     <t>Không</t>
   </si>
   <si>
-    <t>CA002, CA006</t>
+    <t>CA002, CA006, CA026</t>
   </si>
   <si>
     <t>TV005</t>
@@ -854,7 +860,7 @@
     <t>0870482814</t>
   </si>
   <si>
-    <t>CA003, CA021, CA035</t>
+    <t>CA003, CA021, NGOAI_04</t>
   </si>
   <si>
     <t>TV006</t>
@@ -875,7 +881,7 @@
     <t>0848963834</t>
   </si>
   <si>
-    <t>CA005, CA009, CA012, NGOAI_03</t>
+    <t>CA005, CA009, CA012</t>
   </si>
   <si>
     <t>TV007</t>
@@ -890,7 +896,7 @@
     <t>0338299737</t>
   </si>
   <si>
-    <t>CA009, CA011, CA017</t>
+    <t>CA010, CA011, CA017</t>
   </si>
   <si>
     <t>TV008</t>
@@ -905,7 +911,7 @@
     <t>0913267736</t>
   </si>
   <si>
-    <t>CA016, CA032, CA034</t>
+    <t>CA010, CA021, CA034</t>
   </si>
   <si>
     <t>TV009</t>
@@ -914,7 +920,7 @@
     <t>0388208121</t>
   </si>
   <si>
-    <t>CA002, CA021, CA023, CA030</t>
+    <t>CA002, CA030, NGOAI_01</t>
   </si>
   <si>
     <t>TV010</t>
@@ -929,7 +935,7 @@
     <t>0918384251</t>
   </si>
   <si>
-    <t>CA016, CA025</t>
+    <t>CA016, CA025, CA033</t>
   </si>
   <si>
     <t>TV011</t>
@@ -947,7 +953,7 @@
     <t>0959826204</t>
   </si>
   <si>
-    <t>CA026, CA034, NGOAI_04</t>
+    <t>CA026, CA034, CA035</t>
   </si>
   <si>
     <t>TV013</t>
@@ -959,7 +965,7 @@
     <t>0960733754</t>
   </si>
   <si>
-    <t>CA006, CA035</t>
+    <t>CA006, CA033, NGOAI_03</t>
   </si>
   <si>
     <t>TV014</t>
@@ -968,7 +974,7 @@
     <t>0756981693</t>
   </si>
   <si>
-    <t>CA011, CA015, CA024</t>
+    <t>CA015, CA024, CA029</t>
   </si>
   <si>
     <t>TV015</t>
@@ -980,7 +986,7 @@
     <t>0899468044</t>
   </si>
   <si>
-    <t>CA009, CA027, CA033</t>
+    <t>CA004, CA009, CA027</t>
   </si>
   <si>
     <t>TV016</t>
@@ -1004,7 +1010,7 @@
     <t>0387277434</t>
   </si>
   <si>
-    <t>CA012, CA023, CA035</t>
+    <t>CA009, CA012, CA023, CA026</t>
   </si>
   <si>
     <t>TV018</t>
@@ -1019,7 +1025,7 @@
     <t>0303669096</t>
   </si>
   <si>
-    <t>CA008, CA014, CA022</t>
+    <t>CA008, CA014, CA032</t>
   </si>
   <si>
     <t>TV019</t>
@@ -1031,7 +1037,7 @@
     <t>0916272046</t>
   </si>
   <si>
-    <t>CA017, CA030</t>
+    <t>CA013, CA017, CA030, NGOAI_01</t>
   </si>
   <si>
     <t>TV020</t>
@@ -1040,7 +1046,7 @@
     <t>0832719374</t>
   </si>
   <si>
-    <t>CA009, CA025, NGOAI_03</t>
+    <t>CA009, CA025, NGOAI_04</t>
   </si>
   <si>
     <t>TV021</t>
@@ -1061,7 +1067,7 @@
     <t>0350752735</t>
   </si>
   <si>
-    <t>CA003, CA022, CA029</t>
+    <t>CA003, CA025, CA029</t>
   </si>
   <si>
     <t>TV023</t>
@@ -1085,16 +1091,19 @@
     <t>0735240824</t>
   </si>
   <si>
-    <t>CA006, CA019</t>
+    <t>CA006, CA019, CA023</t>
   </si>
   <si>
     <t>TV025</t>
   </si>
   <si>
+    <t>Trần Tuấn Châu</t>
+  </si>
+  <si>
     <t>0894131869</t>
   </si>
   <si>
-    <t>CA004, CA024, NGOAI_01</t>
+    <t>CA024, CA030, NGOAI_01</t>
   </si>
   <si>
     <t>TV026</t>
@@ -1103,7 +1112,7 @@
     <t>0967974034</t>
   </si>
   <si>
-    <t>CA010, CA017, CA031</t>
+    <t>CA017, CA023, CA029, CA031</t>
   </si>
   <si>
     <t>TV027</t>
@@ -1115,19 +1124,16 @@
     <t>0974648877</t>
   </si>
   <si>
-    <t>CA012, CA021, CA026</t>
+    <t>CA012, CA015, CA021</t>
   </si>
   <si>
     <t>TV028</t>
   </si>
   <si>
-    <t>Đặng Bảo Quyên</t>
-  </si>
-  <si>
     <t>0317565512</t>
   </si>
   <si>
-    <t>CA014, CA018, NGOAI_01</t>
+    <t>CA005, CA014, CA018</t>
   </si>
   <si>
     <t>TV029</t>
@@ -1148,7 +1154,7 @@
     <t>0373782639</t>
   </si>
   <si>
-    <t>CA015, CA019, CA023, CA027</t>
+    <t>CA019, CA023, CA027</t>
   </si>
   <si>
     <t>TV031</t>
@@ -1169,7 +1175,7 @@
     <t>0357809134</t>
   </si>
   <si>
-    <t>CA004, CA031</t>
+    <t>CA004, CA015, CA031</t>
   </si>
   <si>
     <t>TV033</t>
@@ -1187,10 +1193,13 @@
     <t>TV034</t>
   </si>
   <si>
+    <t>Phạm Hồng Sơn</t>
+  </si>
+  <si>
     <t>0740640909</t>
   </si>
   <si>
-    <t>CA029, CA030, CA033</t>
+    <t>CA022, CA030, NGOAI_02</t>
   </si>
   <si>
     <t>TV035</t>
@@ -1208,7 +1217,7 @@
     <t>0975496513</t>
   </si>
   <si>
-    <t>CA004, CA005, CA026</t>
+    <t>CA004, CA005, CA018</t>
   </si>
   <si>
     <t>TV037</t>
@@ -1220,7 +1229,7 @@
     <t>0358692617</t>
   </si>
   <si>
-    <t>CA020, CA023, CA028, CA029, CA032</t>
+    <t>CA016, CA020, CA028</t>
   </si>
   <si>
     <t>TV038</t>
@@ -1229,7 +1238,7 @@
     <t>0732931839</t>
   </si>
   <si>
-    <t>CA008, CA025, CA032</t>
+    <t>CA008, CA031, CA032</t>
   </si>
   <si>
     <t>TV039</t>
@@ -1238,16 +1247,19 @@
     <t>0977589178</t>
   </si>
   <si>
-    <t>CA003, NGOAI_04</t>
+    <t>CA003, CA035, NGOAI_03</t>
   </si>
   <si>
     <t>TV040</t>
   </si>
   <si>
+    <t>Trần Đức Quyên</t>
+  </si>
+  <si>
     <t>0849985698</t>
   </si>
   <si>
-    <t>CA008, CA031, CA035</t>
+    <t>CA008, CA035, NGOAI_03</t>
   </si>
   <si>
     <t>TV041</t>
@@ -1259,7 +1271,7 @@
     <t>0311116152</t>
   </si>
   <si>
-    <t>CA001, CA003, CA011, NGOAI_04</t>
+    <t>CA003, CA011, CA035</t>
   </si>
   <si>
     <t>TV042</t>
@@ -1280,7 +1292,7 @@
     <t>0829014767</t>
   </si>
   <si>
-    <t>CA001, CA004, CA011, CA032</t>
+    <t>CA001, CA004, CA011</t>
   </si>
   <si>
     <t>TV044</t>
@@ -1292,7 +1304,7 @@
     <t>0362268388</t>
   </si>
   <si>
-    <t>CA014, CA018, CA020</t>
+    <t>CA001, CA014, CA020, CA032</t>
   </si>
   <si>
     <t>TV045</t>
@@ -1316,16 +1328,19 @@
     <t>0379979955</t>
   </si>
   <si>
-    <t>CA013, CA019, NGOAI_01</t>
+    <t>CA019, CA022, NGOAI_02</t>
   </si>
   <si>
     <t>TV047</t>
   </si>
   <si>
+    <t>Bùi Gia Trang</t>
+  </si>
+  <si>
     <t>0859782071</t>
   </si>
   <si>
-    <t>CA005, CA007, CA022, NGOAI_03</t>
+    <t>CA007, CA022, NGOAI_04</t>
   </si>
   <si>
     <t>TV048</t>
@@ -1346,7 +1361,7 @@
     <t>0718880592</t>
   </si>
   <si>
-    <t>CA015, CA017, CA019</t>
+    <t>CA017, CA019, CA032</t>
   </si>
   <si>
     <t>TV050</t>
@@ -1358,7 +1373,7 @@
     <t>0346886239</t>
   </si>
   <si>
-    <t>CA010, CA013, CA016, CA028</t>
+    <t>CA013, CA016, CA028</t>
   </si>
   <si>
     <t>BẢNG TỔNG HỢP THEO BAN CHUYÊN MÔN</t>
@@ -1409,9 +1424,6 @@
     <t>Vi phạm lịch rảnh đã đăng ký</t>
   </si>
   <si>
-    <t>1 vi phạm</t>
-  </si>
-  <si>
     <t>Tôn trọng lịch rảnh thành viên</t>
   </si>
   <si>
@@ -1436,7 +1448,7 @@
     <t>Độ công bằng phân bổ (Fairness Score)</t>
   </si>
   <si>
-    <t>90.3/100</t>
+    <t>94.8/100</t>
   </si>
   <si>
     <t>Phân bổ đều giữa các thành viên</t>
@@ -1490,7 +1502,7 @@
     <t>Ghi Chú Vắng / Thay Ca</t>
   </si>
   <si>
-    <t>Lý Minh Khang (Chính), Hồ Thị Mai (Chính), Huỳnh Minh Nam (Chính), Huỳnh Thảo Phương (Dự phòng)</t>
+    <t>Lý Minh Khang (Chính), Hoàng Quốc Em (Chính), Huỳnh Minh Nam (Chính), Huỳnh Thảo Phương (Dự phòng)</t>
   </si>
   <si>
     <t>Dương Minh Sơn (0373782639)</t>
@@ -1529,7 +1541,7 @@
     <t>Huỳnh Thảo Phương (0822196937)</t>
   </si>
   <si>
-    <t>Đỗ Hồng Uyên (Chính), Huỳnh Minh Nam (Chính), Trần Đức Khang (Chính), Trần Tuấn Châu (Dự phòng)</t>
+    <t>Đỗ Hồng Uyên (Chính), Huỳnh Minh Nam (Chính), Trần Đức Khang (Chính), Hồ Nhật Uyên (Dự phòng)</t>
   </si>
   <si>
     <t>Huỳnh Thị Uyên (0851925462)</t>
@@ -1538,127 +1550,124 @@
     <t>Phạm Minh Yến (0379979955)</t>
   </si>
   <si>
-    <t>Võ Thị Dung (0358692617)</t>
-  </si>
-  <si>
-    <t>Bùi Gia Trang (Chính), Đỗ Hồng Uyên (Chính), Lê Hải Yến (Chính), Võ Tuấn Châu (Dự phòng)</t>
+    <t>Trần Tuấn Châu (0894131869)</t>
+  </si>
+  <si>
+    <t>Đặng Bảo Quyên (Chính), Đỗ Hồng Uyên (Chính), Lê Hải Yến (Chính), Võ Tuấn Châu (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Bùi Gia Trang (0859782071)</t>
+  </si>
+  <si>
+    <t>Hồ Minh Quyên (0916272046)</t>
+  </si>
+  <si>
+    <t>Huỳnh Minh Nam (0829014767)</t>
+  </si>
+  <si>
+    <t>Hoàng Minh Hương (Chính), Đỗ Thị Anh (Chính), Nguyễn Minh Mai (Chính), Võ Nhật Vinh (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Đặng Quốc Dung (0387277434)</t>
+  </si>
+  <si>
+    <t>Đỗ Thị Giang (0967974034)</t>
+  </si>
+  <si>
+    <t>Bùi Thảo Châu (Chính), Huỳnh Quốc Khang (Chính), Bùi Gia Trang (Chính), Huỳnh Thảo Phương (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Hết nhân sự rảnh</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Dương Tuấn Quyên (Chính), Hồ Quốc Châu (Chính), Huỳnh Quốc Khang (Chính), Trần Đức Quyên (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Hồ Hồng Uyên (0959826204)</t>
+  </si>
+  <si>
+    <t>Phạm Hồng Sơn (0740640909)</t>
+  </si>
+  <si>
+    <t>Hồ Nhật Uyên (Chính), Đặng Quốc Dung (Chính), Đỗ Thị Bình (Chính), Võ Tuấn Châu (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Hồ Thị Mai (0311116152)</t>
+  </si>
+  <si>
+    <t>Võ Bảo Sơn (Chính), Dương Ngọc Nam (Chính), Trần Hoàng Bình (Chính), Lê Nhật Quyên (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Hồ Thị Mai (Chính), Huỳnh Minh Nam (Chính), Huỳnh Quốc Khang (Chính), Trần Hoàng Bình (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Nguyễn Gia Nam (Chính), Đặng Quốc Dung (Chính), Nguyễn Minh Linh (Chính), Võ Tuấn Châu (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Võ Bảo Sơn (Chính), Hồ Minh Quyên (Chính), Đỗ Thị Anh (Chính), Lý Tuấn Hà (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Đỗ Hồng Uyên (0975496513)</t>
+  </si>
+  <si>
+    <t>Lý Minh Khang (Chính), Đặng Bảo Quyên (Chính), Hoàng Quốc Em (Chính), Hồ Quốc Châu (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Hồ Ngọc Bình (0388208121)</t>
+  </si>
+  <si>
+    <t>Huỳnh Thị Uyên (Chính), Lê Gia Khang (Chính), Nguyễn Minh Linh (Chính), Trần Đức Khang (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Hồ Hải Linh (0351850671)</t>
+  </si>
+  <si>
+    <t>Hồ Hải Linh (Chính), Lý Tuấn Hà (Chính), Võ Thị Dung (Chính), Vũ Minh Linh (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Đỗ Thị Giang (Chính), Hồ Minh Quyên (Chính), Huỳnh Hải Sơn (Chính), Trần Hoàng Bình (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Đỗ Tuấn Uyên (Chính), Nguyễn Gia Nam (Chính), Đặng Bảo Quyên (Chính), Đỗ Hồng Uyên (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Dương Minh Sơn (Chính), Huỳnh Hải Sơn (Chính), Phạm Minh Yến (Chính), Võ Nhật Vinh (Dự phòng)</t>
   </si>
   <si>
     <t>Đặng Bảo Quyên (0317565512)</t>
   </si>
   <si>
-    <t>Hồ Minh Quyên (0916272046)</t>
-  </si>
-  <si>
-    <t>Huỳnh Minh Nam (0829014767)</t>
-  </si>
-  <si>
-    <t>Hoàng Minh Hương (Chính), Đỗ Thị Anh (Chính), Nguyễn Minh Mai (Chính), Võ Nhật Vinh (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Đặng Quốc Dung (0387277434)</t>
-  </si>
-  <si>
-    <t>Đỗ Thị Giang (0967974034)</t>
-  </si>
-  <si>
-    <t>Bùi Thảo Châu (Chính), Huỳnh Quốc Khang (Chính), Bùi Gia Trang (Chính), Huỳnh Thảo Phương (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Hết nhân sự rảnh</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Dương Tuấn Quyên (Chính), Hồ Quốc Châu (Chính), Huỳnh Quốc Khang (Chính), Trần Đức Quyên (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Hồ Hồng Uyên (0959826204)</t>
-  </si>
-  <si>
-    <t>Phạm Hồng Sơn (0740640909)</t>
-  </si>
-  <si>
-    <t>Hồ Nhật Uyên (Chính), Đỗ Thị Bình (Chính), Trần Hoàng Bình (Chính), Võ Tuấn Châu (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Võ Bảo Sơn (Chính), Dương Ngọc Nam (Chính), Đỗ Thị Giang (Chính), Lý Tuấn Hà (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Hồ Thị Mai (Chính), Huỳnh Minh Nam (Chính), Lê Gia Khang (Chính), Trần Hoàng Bình (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Huỳnh Quốc Khang (0827648350)</t>
-  </si>
-  <si>
-    <t>Nguyễn Gia Nam (Chính), Đặng Quốc Dung (Chính), Nguyễn Minh Linh (Chính), Võ Tuấn Châu (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Hồ Thị Mai (0311116152)</t>
-  </si>
-  <si>
-    <t>Võ Bảo Sơn (Chính), Đỗ Thị Anh (Chính), Lý Tuấn Hà (Chính), Phạm Minh Yến (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Bùi Gia Trang (0859782071)</t>
-  </si>
-  <si>
-    <t>Đỗ Hồng Uyên (0975496513)</t>
-  </si>
-  <si>
-    <t>Lý Minh Khang (Chính), Đặng Bảo Quyên (Chính), Hoàng Quốc Em (Chính), Hồ Quốc Châu (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Hồ Ngọc Bình (0388208121)</t>
-  </si>
-  <si>
-    <t>Dương Minh Sơn (Chính), Huỳnh Thị Uyên (Chính), Lê Gia Khang (Chính), Huỳnh Hải Sơn (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Hồ Hải Linh (0351850671)</t>
-  </si>
-  <si>
-    <t>Lê Nhật Quyên (Chính), Hồ Hải Linh (Chính), Lý Tuấn Hà (Chính), Vũ Minh Linh (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Đỗ Thị Giang (Chính), Hồ Minh Quyên (Chính), Huỳnh Hải Sơn (Chính), Trần Hoàng Bình (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Đỗ Tuấn Uyên (Chính), Nguyễn Gia Nam (Chính), Đặng Bảo Quyên (Chính), Hoàng Quốc Em (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Dương Minh Sơn (Chính), Huỳnh Hải Sơn (Chính), Phạm Minh Yến (Chính), Võ Nhật Vinh (Dự phòng)</t>
-  </si>
-  <si>
     <t>Đỗ Tuấn Uyên (Chính), Hoàng Quốc Em (Chính), Hồ Hải Linh (Chính), Võ Thị Dung (Dự phòng)</t>
   </si>
   <si>
     <t>Huỳnh Hải Sơn (0718880592)</t>
   </si>
   <si>
-    <t>Lý Ngọc Khang (Chính), Hồ Ngọc Bình (Chính), Lê Hải Yến (Chính), Nguyễn Minh Linh (Dự phòng)</t>
+    <t>Lý Ngọc Khang (Chính), Lê Hải Yến (Chính), Lê Nhật Quyên (Chính), Nguyễn Minh Linh (Dự phòng)</t>
   </si>
   <si>
     <t>Hồ Quốc Châu (0303669096)</t>
   </si>
   <si>
-    <t>Dương Quốc Châu (Chính), Bùi Gia Trang (Chính), Lý Thảo Hà (Chính), Hồ Quốc Châu (Dự phòng)</t>
+    <t>Bùi Gia Trang (Chính), Lý Thảo Hà (Chính), Phạm Hồng Sơn (Chính), Phạm Minh Yến (Dự phòng)</t>
   </si>
   <si>
     <t>Hoàng Quốc Em (0362268388)</t>
   </si>
   <si>
-    <t>Dương Minh Sơn (Chính), Đặng Quốc Dung (Chính), Hồ Ngọc Bình (Chính), Võ Thị Dung (Dự phòng)</t>
+    <t>Dương Minh Sơn (Chính), Đặng Quốc Dung (Chính), Đỗ Thị Giang (Chính), Võ Nhật Vinh (Dự phòng)</t>
   </si>
   <si>
     <t>Huỳnh Thảo Phương (Chính), Huỳnh Thị Uyên (Chính), Trần Tuấn Châu (Chính), Lê Gia Khang (Dự phòng)</t>
   </si>
   <si>
-    <t>Đỗ Thị Bình (Chính), Vũ Minh Linh (Chính), Dương Tuấn Quyên (Chính), Đỗ Thị Anh (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Đỗ Tuấn Uyên (Chính), Đỗ Hồng Uyên (Chính), Hồ Hồng Uyên (Chính), Nguyễn Minh Linh (Dự phòng)</t>
+    <t>Dương Quốc Châu (Chính), Đỗ Thị Bình (Chính), Vũ Minh Linh (Chính), Đỗ Thị Anh (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Đỗ Tuấn Uyên (Chính), Đặng Quốc Dung (Chính), Hồ Hồng Uyên (Chính), Hoàng Minh Hương (Dự phòng)</t>
   </si>
   <si>
     <t>Hồ Nhật Uyên (Chính), Võ Bảo Sơn (Chính), Huỳnh Thị Uyên (Chính), Dương Minh Sơn (Dự phòng)</t>
@@ -1667,19 +1676,19 @@
     <t>Dương Ngọc Nam (Chính), Lý Thảo Hà (Chính), Lý Tuấn Hà (Chính), Võ Thị Dung (Dự phòng)</t>
   </si>
   <si>
-    <t>Dương Quốc Châu (Chính), Lê Hải Yến (Chính), Phạm Hồng Sơn (Chính), Võ Thị Dung (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Hồ Minh Quyên (Chính), Hồ Ngọc Bình (Chính), Lê Quốc Mai (Chính), Phạm Hồng Sơn (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Đỗ Thị Giang (Chính), Lý Thảo Hà (Chính), Trần Đức Khang (Chính), Trần Đức Quyên (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Dương Tuấn Quyên (Chính), Võ Thị Dung (Chính), Lê Nhật Quyên (Chính), Huỳnh Minh Nam (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Bùi Thảo Châu (Chính), Lê Quốc Mai (Chính), Phạm Hồng Sơn (Chính), Hồ Nhật Uyên (Dự phòng)</t>
+    <t>Dương Quốc Châu (Chính), Đỗ Thị Giang (Chính), Lê Gia Khang (Chính), Lê Hải Yến (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Hồ Minh Quyên (Chính), Hồ Ngọc Bình (Chính), Phạm Hồng Sơn (Chính), Trần Tuấn Châu (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Dương Tuấn Quyên (Chính), Đỗ Thị Giang (Chính), Lý Thảo Hà (Chính), Trần Đức Khang (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Dương Tuấn Quyên (Chính), Hoàng Quốc Em (Chính), Hồ Quốc Châu (Chính), Huỳnh Hải Sơn (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Bùi Thảo Châu (Chính), Lê Quốc Mai (Chính), Nguyễn Minh Mai (Chính), Vũ Minh Linh (Dự phòng)</t>
   </si>
   <si>
     <t>Lê Nhật Quyên (Chính), Bùi Thảo Châu (Chính), Hồ Hải Linh (Chính), Hồ Hồng Uyên (Dự phòng)</t>
@@ -1691,16 +1700,19 @@
     <t>Võ Bảo Sơn (0334957885)</t>
   </si>
   <si>
-    <t>Trần Đức Quyên (Chính), Lý Ngọc Khang (Chính), Đặng Quốc Dung (Chính), Nguyễn Minh Mai (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Trần Tuấn Châu (Chính), Đặng Bảo Quyên (Chính), Phạm Minh Yến (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Bùi Gia Trang (Chính), Đỗ Thị Bình (Chính), Võ Tuấn Châu (Dự phòng)</t>
-  </si>
-  <si>
-    <t>Nguyễn Minh Khang (Chính), Hồ Hồng Uyên (Chính), Hồ Thị Mai (Dự phòng)</t>
+    <t>Nguyễn Minh Khang (Chính), Hồ Hồng Uyên (Chính), Hồ Thị Mai (Chính), Trần Đức Quyên (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Hồ Minh Quyên (Chính), Hồ Ngọc Bình (Chính), Trần Tuấn Châu (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Lê Quốc Mai (Chính), Phạm Hồng Sơn (Chính), Phạm Minh Yến (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Khang (Chính), Trần Đức Quyên (Chính), Nguyễn Minh Mai (Dự phòng)</t>
+  </si>
+  <si>
+    <t>Lý Ngọc Khang (Chính), Bùi Gia Trang (Chính), Đỗ Thị Bình (Dự phòng)</t>
   </si>
 </sst>
 </file>
@@ -2343,7 +2355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="11" width="55" customWidth="1"/>
@@ -2790,10 +2802,10 @@
         <v>4</v>
       </c>
       <c r="I15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>21</v>
@@ -2801,7 +2813,7 @@
     </row>
     <row r="16" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>14</v>
@@ -2825,10 +2837,10 @@
         <v>4</v>
       </c>
       <c r="I16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J16" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>21</v>
@@ -2836,7 +2848,7 @@
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>14</v>
@@ -2860,10 +2872,10 @@
         <v>4</v>
       </c>
       <c r="I17" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>21</v>
@@ -2871,7 +2883,7 @@
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>14</v>
@@ -2898,7 +2910,7 @@
         <v>19</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>21</v>
@@ -2906,7 +2918,7 @@
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>14</v>
@@ -2930,10 +2942,10 @@
         <v>4</v>
       </c>
       <c r="I19" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J19" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="K19" s="6" t="s">
         <v>21</v>
@@ -2941,16 +2953,16 @@
     </row>
     <row r="20" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="4" t="s">
+      <c r="D20" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>17</v>
@@ -2965,10 +2977,10 @@
         <v>4</v>
       </c>
       <c r="I20" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J20" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>74</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>21</v>
@@ -2976,16 +2988,16 @@
     </row>
     <row r="21" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>23</v>
@@ -3000,10 +3012,10 @@
         <v>4</v>
       </c>
       <c r="I21" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J21" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>21</v>
@@ -3011,16 +3023,16 @@
     </row>
     <row r="22" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>27</v>
@@ -3035,10 +3047,10 @@
         <v>4</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>21</v>
@@ -3046,16 +3058,16 @@
     </row>
     <row r="23" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>31</v>
@@ -3070,7 +3082,7 @@
         <v>4</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>81</v>
@@ -3087,10 +3099,10 @@
         <v>14</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>35</v>
@@ -3105,7 +3117,7 @@
         <v>4</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>83</v>
@@ -3210,7 +3222,7 @@
         <v>4</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>92</v>
@@ -3245,10 +3257,10 @@
         <v>4</v>
       </c>
       <c r="I28" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J28" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>21</v>
@@ -3256,7 +3268,7 @@
     </row>
     <row r="29" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>14</v>
@@ -3283,7 +3295,7 @@
         <v>49</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>21</v>
@@ -3291,16 +3303,16 @@
     </row>
     <row r="30" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="4" t="s">
+      <c r="D30" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>100</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>17</v>
@@ -3315,10 +3327,10 @@
         <v>4</v>
       </c>
       <c r="I30" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="J30" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>102</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>21</v>
@@ -3326,16 +3338,16 @@
     </row>
     <row r="31" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C31" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>100</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>23</v>
@@ -3350,10 +3362,10 @@
         <v>4</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>21</v>
@@ -3361,16 +3373,16 @@
     </row>
     <row r="32" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C32" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>100</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>27</v>
@@ -3388,7 +3400,7 @@
         <v>52</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>21</v>
@@ -3396,16 +3408,16 @@
     </row>
     <row r="33" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C33" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>100</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>31</v>
@@ -3420,10 +3432,10 @@
         <v>4</v>
       </c>
       <c r="I33" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="J33" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>21</v>
@@ -3431,16 +3443,16 @@
     </row>
     <row r="34" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C34" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>100</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>35</v>
@@ -3455,10 +3467,10 @@
         <v>4</v>
       </c>
       <c r="I34" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J34" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="J34" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>21</v>
@@ -3466,16 +3478,16 @@
     </row>
     <row r="35" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="4" t="s">
+      <c r="D35" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>115</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>17</v>
@@ -3490,10 +3502,10 @@
         <v>4</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>21</v>
@@ -3501,16 +3513,16 @@
     </row>
     <row r="36" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C36" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>115</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>23</v>
@@ -3528,7 +3540,7 @@
         <v>46</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>21</v>
@@ -3536,16 +3548,16 @@
     </row>
     <row r="37" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>115</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>27</v>
@@ -3560,10 +3572,10 @@
         <v>4</v>
       </c>
       <c r="I37" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J37" s="5" t="s">
         <v>120</v>
-      </c>
-      <c r="J37" s="5" t="s">
-        <v>121</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>21</v>
@@ -3571,16 +3583,16 @@
     </row>
     <row r="38" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C38" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>115</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>31</v>
@@ -3595,10 +3607,10 @@
         <v>4</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>21</v>
@@ -3606,16 +3618,16 @@
     </row>
     <row r="39" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C39" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>115</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>35</v>
@@ -3630,10 +3642,10 @@
         <v>4</v>
       </c>
       <c r="I39" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J39" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="J39" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>21</v>
@@ -3641,34 +3653,34 @@
     </row>
     <row r="40" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="C40" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E40" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C40" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E40" s="7" t="s">
+      <c r="F40" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="G40" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G40" s="7" t="s">
+      <c r="H40" s="7">
+        <v>3</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="J40" s="8" t="s">
         <v>131</v>
-      </c>
-      <c r="H40" s="7">
-        <v>3</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="J40" s="8" t="s">
-        <v>133</v>
       </c>
       <c r="K40" s="9" t="s">
         <v>21</v>
@@ -3676,34 +3688,34 @@
     </row>
     <row r="41" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F41" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="F41" s="8" t="s">
+      <c r="G41" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H41" s="7">
+        <v>3</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="J41" s="8" t="s">
         <v>135</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="H41" s="7">
-        <v>3</v>
-      </c>
-      <c r="I41" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J41" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="K41" s="9" t="s">
         <v>21</v>
@@ -3711,36 +3723,71 @@
     </row>
     <row r="42" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H42" s="7">
+        <v>3</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="J42" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C42" s="7" t="s">
+      <c r="K42" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D43" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D42" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="F42" s="8" t="s">
+      <c r="E43" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="G42" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="H42" s="7">
-        <v>3</v>
-      </c>
-      <c r="I42" s="8" t="s">
+      <c r="F43" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="J42" s="8" t="s">
+      <c r="G43" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H43" s="7">
+        <v>3</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J43" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="K42" s="9" t="s">
+      <c r="K43" s="9" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4114,7 +4161,7 @@
         <v>4</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="H14" s="12" t="s">
         <v>159</v>
@@ -4125,7 +4172,7 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>55</v>
@@ -4143,7 +4190,7 @@
         <v>4</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H15" s="14" t="s">
         <v>160</v>
@@ -4154,7 +4201,7 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>55</v>
@@ -4172,7 +4219,7 @@
         <v>4</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>161</v>
@@ -4183,7 +4230,7 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>55</v>
@@ -4212,7 +4259,7 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>55</v>
@@ -4230,7 +4277,7 @@
         <v>4</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>163</v>
@@ -4241,13 +4288,13 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="C19" s="13" t="s">
         <v>71</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>72</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>17</v>
@@ -4259,7 +4306,7 @@
         <v>4</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H19" s="14" t="s">
         <v>164</v>
@@ -4270,13 +4317,13 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>71</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>72</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>23</v>
@@ -4288,7 +4335,7 @@
         <v>4</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H20" s="12" t="s">
         <v>165</v>
@@ -4299,13 +4346,13 @@
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B21" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>71</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>72</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>27</v>
@@ -4317,7 +4364,7 @@
         <v>4</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H21" s="14" t="s">
         <v>166</v>
@@ -4328,13 +4375,13 @@
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B22" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>71</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>72</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>31</v>
@@ -4346,7 +4393,7 @@
         <v>4</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>167</v>
@@ -4360,10 +4407,10 @@
         <v>82</v>
       </c>
       <c r="B23" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>71</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>72</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>35</v>
@@ -4375,7 +4422,7 @@
         <v>4</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H23" s="14" t="s">
         <v>168</v>
@@ -4462,7 +4509,7 @@
         <v>4</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>171</v>
@@ -4491,7 +4538,7 @@
         <v>4</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="H27" s="14" t="s">
         <v>172</v>
@@ -4502,7 +4549,7 @@
     </row>
     <row r="28" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>85</v>
@@ -4531,13 +4578,13 @@
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="C29" s="13" t="s">
         <v>99</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>100</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>17</v>
@@ -4549,7 +4596,7 @@
         <v>4</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H29" s="14" t="s">
         <v>174</v>
@@ -4560,13 +4607,13 @@
     </row>
     <row r="30" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B30" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" s="11" t="s">
         <v>99</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>100</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>23</v>
@@ -4578,7 +4625,7 @@
         <v>4</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>175</v>
@@ -4589,13 +4636,13 @@
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B31" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>99</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>100</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>27</v>
@@ -4618,13 +4665,13 @@
     </row>
     <row r="32" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B32" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" s="11" t="s">
         <v>99</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>100</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>31</v>
@@ -4636,7 +4683,7 @@
         <v>4</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>177</v>
@@ -4647,13 +4694,13 @@
     </row>
     <row r="33" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B33" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" s="13" t="s">
         <v>99</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>100</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>35</v>
@@ -4665,7 +4712,7 @@
         <v>4</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H33" s="14" t="s">
         <v>178</v>
@@ -4676,13 +4723,13 @@
     </row>
     <row r="34" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B34" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="C34" s="11" t="s">
         <v>114</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>115</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>17</v>
@@ -4694,7 +4741,7 @@
         <v>4</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>179</v>
@@ -4705,13 +4752,13 @@
     </row>
     <row r="35" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B35" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" s="13" t="s">
         <v>114</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>115</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>23</v>
@@ -4734,13 +4781,13 @@
     </row>
     <row r="36" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B36" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C36" s="11" t="s">
         <v>114</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>115</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>27</v>
@@ -4752,7 +4799,7 @@
         <v>4</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H36" s="12" t="s">
         <v>181</v>
@@ -4763,13 +4810,13 @@
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B37" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C37" s="13" t="s">
         <v>114</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>115</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>31</v>
@@ -4781,7 +4828,7 @@
         <v>4</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H37" s="14" t="s">
         <v>182</v>
@@ -4792,13 +4839,13 @@
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B38" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C38" s="11" t="s">
         <v>114</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>115</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>35</v>
@@ -4810,7 +4857,7 @@
         <v>4</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H38" s="12" t="s">
         <v>183</v>
@@ -4830,7 +4877,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="8" width="50" customWidth="1"/>
@@ -4881,28 +4928,28 @@
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>100</v>
-      </c>
       <c r="D4" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="F4" s="11" t="s">
-        <v>131</v>
-      </c>
       <c r="G4" s="11">
         <v>3</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>189</v>
@@ -4910,28 +4957,28 @@
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>135</v>
-      </c>
       <c r="F5" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G5" s="7">
         <v>3</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>190</v>
@@ -4939,31 +4986,60 @@
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B6" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>115</v>
-      </c>
       <c r="D6" s="11" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G6" s="11">
         <v>3</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>191</v>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G7" s="7">
+        <v>3</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -4985,7 +5061,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -5002,66 +5078,66 @@
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L3" s="18" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H4" s="19">
         <v>3</v>
@@ -5079,30 +5155,30 @@
         <v>1</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H5" s="20">
         <v>3</v>
@@ -5111,89 +5187,89 @@
         <v>6</v>
       </c>
       <c r="J5" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="13">
         <v>3</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>43</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H6" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="19">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J6" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" s="11">
         <v>0</v>
       </c>
       <c r="L6" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H7" s="20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" s="20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J7" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" s="13">
         <v>0</v>
@@ -5202,30 +5278,30 @@
         <v>2</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H8" s="19">
         <v>3</v>
@@ -5234,80 +5310,80 @@
         <v>6</v>
       </c>
       <c r="J8" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="11">
         <v>2</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H9" s="20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9" s="20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J9" s="13">
         <v>3</v>
       </c>
       <c r="K9" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="13">
         <v>3</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H10" s="19">
         <v>3</v>
@@ -5325,30 +5401,30 @@
         <v>3</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H11" s="20">
         <v>3</v>
@@ -5363,115 +5439,115 @@
         <v>0</v>
       </c>
       <c r="L11" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H12" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I12" s="19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J12" s="11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K12" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H13" s="20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13" s="20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J13" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" s="13">
         <v>0</v>
       </c>
       <c r="L13" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M13" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>19</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H14" s="19">
         <v>2</v>
@@ -5489,30 +5565,30 @@
         <v>2</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H15" s="20">
         <v>3</v>
@@ -5521,80 +5597,80 @@
         <v>6</v>
       </c>
       <c r="J15" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="13">
         <v>3</v>
       </c>
       <c r="M15" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H16" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" s="19">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J16" s="11">
         <v>2</v>
       </c>
       <c r="K16" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" s="12" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H17" s="20">
         <v>3</v>
@@ -5612,30 +5688,30 @@
         <v>2</v>
       </c>
       <c r="M17" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H18" s="19">
         <v>3</v>
@@ -5653,30 +5729,30 @@
         <v>2</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H19" s="20">
         <v>3</v>
@@ -5694,71 +5770,71 @@
         <v>3</v>
       </c>
       <c r="M19" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H20" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" s="19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J20" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" s="11">
         <v>0</v>
       </c>
       <c r="L20" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H21" s="20">
         <v>3</v>
@@ -5776,71 +5852,71 @@
         <v>2</v>
       </c>
       <c r="M21" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H22" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I22" s="19">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J22" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M22" s="12" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>49</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H23" s="20">
         <v>3</v>
@@ -5858,30 +5934,30 @@
         <v>2</v>
       </c>
       <c r="M23" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H24" s="19">
         <v>3</v>
@@ -5899,30 +5975,30 @@
         <v>3</v>
       </c>
       <c r="M24" s="12" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H25" s="20">
         <v>3</v>
@@ -5940,30 +6016,30 @@
         <v>3</v>
       </c>
       <c r="M25" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H26" s="19">
         <v>3</v>
@@ -5981,71 +6057,71 @@
         <v>3</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H27" s="20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27" s="20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J27" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="13">
         <v>0</v>
       </c>
       <c r="L27" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M27" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>132</v>
+        <v>309</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H28" s="19">
         <v>3</v>
@@ -6060,74 +6136,74 @@
         <v>1</v>
       </c>
       <c r="L28" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H29" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29" s="20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J29" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" s="13">
         <v>0</v>
       </c>
       <c r="L29" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M29" s="14" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H30" s="19">
         <v>3</v>
@@ -6145,30 +6221,30 @@
         <v>2</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H31" s="20">
         <v>3</v>
@@ -6177,39 +6253,39 @@
         <v>6</v>
       </c>
       <c r="J31" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M31" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H32" s="19">
         <v>3</v>
@@ -6227,71 +6303,71 @@
         <v>3</v>
       </c>
       <c r="M32" s="12" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H33" s="20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I33" s="20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J33" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K33" s="13">
         <v>0</v>
       </c>
       <c r="L33" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M33" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>89</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H34" s="19">
         <v>3</v>
@@ -6309,71 +6385,71 @@
         <v>3</v>
       </c>
       <c r="M34" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H35" s="20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" s="20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J35" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K35" s="13">
         <v>0</v>
       </c>
       <c r="L35" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M35" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H36" s="19">
         <v>3</v>
@@ -6391,30 +6467,30 @@
         <v>1</v>
       </c>
       <c r="M36" s="12" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>108</v>
+        <v>341</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H37" s="20">
         <v>3</v>
@@ -6423,39 +6499,39 @@
         <v>6</v>
       </c>
       <c r="J37" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K37" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="13">
         <v>3</v>
       </c>
       <c r="M37" s="14" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H38" s="19">
         <v>2</v>
@@ -6473,30 +6549,30 @@
         <v>2</v>
       </c>
       <c r="M38" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>32</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H39" s="20">
         <v>3</v>
@@ -6514,71 +6590,71 @@
         <v>3</v>
       </c>
       <c r="M39" s="14" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H40" s="19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I40" s="19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J40" s="11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K40" s="11">
         <v>0</v>
       </c>
       <c r="L40" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M40" s="12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>46</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H41" s="20">
         <v>3</v>
@@ -6593,74 +6669,74 @@
         <v>0</v>
       </c>
       <c r="L41" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M41" s="14" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H42" s="19">
+        <v>3</v>
+      </c>
+      <c r="I42" s="19">
+        <v>6</v>
+      </c>
+      <c r="J42" s="11">
         <v>2</v>
-      </c>
-      <c r="I42" s="19">
-        <v>4</v>
-      </c>
-      <c r="J42" s="11">
-        <v>1</v>
       </c>
       <c r="K42" s="11">
         <v>1</v>
       </c>
       <c r="L42" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M42" s="12" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>125</v>
+        <v>361</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H43" s="20">
         <v>3</v>
@@ -6669,80 +6745,80 @@
         <v>6</v>
       </c>
       <c r="J43" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K43" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="13">
         <v>3</v>
       </c>
       <c r="M43" s="14" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H44" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I44" s="19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J44" s="11">
         <v>3</v>
       </c>
       <c r="K44" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="11">
         <v>3</v>
       </c>
       <c r="M44" s="12" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>52</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H45" s="20">
         <v>3</v>
@@ -6760,39 +6836,39 @@
         <v>3</v>
       </c>
       <c r="M45" s="14" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H46" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I46" s="19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J46" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K46" s="11">
         <v>0</v>
@@ -6801,71 +6877,71 @@
         <v>2</v>
       </c>
       <c r="M46" s="12" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H47" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I47" s="20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J47" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K47" s="13">
         <v>0</v>
       </c>
       <c r="L47" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M47" s="14" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H48" s="19">
         <v>3</v>
@@ -6883,30 +6959,30 @@
         <v>3</v>
       </c>
       <c r="M48" s="12" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H49" s="20">
         <v>3</v>
@@ -6921,74 +6997,74 @@
         <v>1</v>
       </c>
       <c r="L49" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M49" s="14" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>36</v>
+        <v>388</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H50" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I50" s="19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J50" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K50" s="11">
         <v>1</v>
       </c>
       <c r="L50" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M50" s="12" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H51" s="20">
         <v>3</v>
@@ -7006,30 +7082,30 @@
         <v>3</v>
       </c>
       <c r="M51" s="14" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H52" s="19">
         <v>3</v>
@@ -7047,39 +7123,39 @@
         <v>2</v>
       </c>
       <c r="M52" s="12" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H53" s="20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I53" s="20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J53" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K53" s="13">
         <v>0</v>
@@ -7088,31 +7164,31 @@
         <v>2</v>
       </c>
       <c r="M53" s="14" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="21" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="22" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B57" s="22" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D57" s="22" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="23" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B58" s="24">
         <v>10</v>
@@ -7126,21 +7202,21 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="23" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B59" s="24">
         <v>10</v>
       </c>
       <c r="C59" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D59" s="24">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="23" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B60" s="24">
         <v>3</v>
@@ -7154,7 +7230,7 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="23" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B61" s="24">
         <v>8</v>
@@ -7168,30 +7244,30 @@
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B62" s="24">
         <v>9</v>
       </c>
       <c r="C62" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D62" s="24">
-        <v>3.11</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="23" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B63" s="24">
         <v>10</v>
       </c>
       <c r="C63" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D63" s="24">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>
@@ -7205,7 +7281,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="8" width="55" customWidth="1"/>
@@ -7213,7 +7289,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -7225,7 +7301,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B3" s="21"/>
       <c r="C3" s="21"/>
@@ -7233,91 +7309,91 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B6" s="28" t="s">
         <v>414</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
+        <v>419</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>420</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="D7" s="29" t="s">
         <v>416</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>417</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>418</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="27" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
@@ -7332,7 +7408,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>4</v>
@@ -7341,16 +7417,16 @@
         <v>6</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>9</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7373,10 +7449,10 @@
         <v>4</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7399,10 +7475,10 @@
         <v>4</v>
       </c>
       <c r="G15" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7425,10 +7501,10 @@
         <v>4</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7451,10 +7527,10 @@
         <v>4</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7477,10 +7553,10 @@
         <v>4</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7503,10 +7579,10 @@
         <v>4</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7529,10 +7605,10 @@
         <v>4</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7555,10 +7631,10 @@
         <v>4</v>
       </c>
       <c r="G21" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7581,10 +7657,10 @@
         <v>4</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7607,10 +7683,10 @@
         <v>4</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7633,15 +7709,15 @@
         <v>4</v>
       </c>
       <c r="G24" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B25" s="24" t="s">
         <v>14</v>
@@ -7659,15 +7735,15 @@
         <v>4</v>
       </c>
       <c r="G25" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B26" s="24" t="s">
         <v>14</v>
@@ -7685,15 +7761,15 @@
         <v>4</v>
       </c>
       <c r="G26" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B27" s="24" t="s">
         <v>14</v>
@@ -7711,15 +7787,15 @@
         <v>4</v>
       </c>
       <c r="G27" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B28" s="24" t="s">
         <v>14</v>
@@ -7737,21 +7813,21 @@
         <v>4</v>
       </c>
       <c r="G28" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H28" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="24" t="s">
         <v>70</v>
-      </c>
-      <c r="B29" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>71</v>
       </c>
       <c r="D29" s="24" t="s">
         <v>17</v>
@@ -7763,21 +7839,21 @@
         <v>4</v>
       </c>
       <c r="G29" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H29" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B30" s="24" t="s">
         <v>14</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D30" s="24" t="s">
         <v>23</v>
@@ -7789,21 +7865,21 @@
         <v>4</v>
       </c>
       <c r="G30" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B31" s="24" t="s">
         <v>14</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D31" s="24" t="s">
         <v>27</v>
@@ -7815,21 +7891,21 @@
         <v>4</v>
       </c>
       <c r="G31" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B32" s="24" t="s">
         <v>14</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D32" s="24" t="s">
         <v>31</v>
@@ -7841,10 +7917,10 @@
         <v>4</v>
       </c>
       <c r="G32" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7855,7 +7931,7 @@
         <v>14</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D33" s="24" t="s">
         <v>35</v>
@@ -7867,10 +7943,10 @@
         <v>4</v>
       </c>
       <c r="G33" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H33" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7893,10 +7969,10 @@
         <v>4</v>
       </c>
       <c r="G34" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H34" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7919,10 +7995,10 @@
         <v>4</v>
       </c>
       <c r="G35" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H35" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7945,10 +8021,10 @@
         <v>4</v>
       </c>
       <c r="G36" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H36" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7971,15 +8047,15 @@
         <v>4</v>
       </c>
       <c r="G37" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H37" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B38" s="24" t="s">
         <v>14</v>
@@ -7997,21 +8073,21 @@
         <v>4</v>
       </c>
       <c r="G38" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H38" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="24" t="s">
         <v>98</v>
-      </c>
-      <c r="B39" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="C39" s="24" t="s">
-        <v>99</v>
       </c>
       <c r="D39" s="24" t="s">
         <v>17</v>
@@ -8023,21 +8099,21 @@
         <v>4</v>
       </c>
       <c r="G39" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H39" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B40" s="24" t="s">
         <v>14</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D40" s="24" t="s">
         <v>23</v>
@@ -8049,21 +8125,21 @@
         <v>4</v>
       </c>
       <c r="G40" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B41" s="24" t="s">
         <v>14</v>
       </c>
       <c r="C41" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D41" s="24" t="s">
         <v>27</v>
@@ -8075,21 +8151,21 @@
         <v>4</v>
       </c>
       <c r="G41" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H41" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B42" s="24" t="s">
         <v>14</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D42" s="24" t="s">
         <v>31</v>
@@ -8101,21 +8177,21 @@
         <v>4</v>
       </c>
       <c r="G42" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H42" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B43" s="24" t="s">
         <v>14</v>
       </c>
       <c r="C43" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D43" s="24" t="s">
         <v>35</v>
@@ -8127,21 +8203,21 @@
         <v>4</v>
       </c>
       <c r="G43" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B44" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="24" t="s">
         <v>113</v>
-      </c>
-      <c r="B44" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="C44" s="24" t="s">
-        <v>114</v>
       </c>
       <c r="D44" s="24" t="s">
         <v>17</v>
@@ -8153,21 +8229,21 @@
         <v>4</v>
       </c>
       <c r="G44" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B45" s="24" t="s">
         <v>14</v>
       </c>
       <c r="C45" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D45" s="24" t="s">
         <v>23</v>
@@ -8179,21 +8255,21 @@
         <v>4</v>
       </c>
       <c r="G45" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="24" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B46" s="24" t="s">
         <v>14</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D46" s="24" t="s">
         <v>27</v>
@@ -8205,21 +8281,21 @@
         <v>4</v>
       </c>
       <c r="G46" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B47" s="24" t="s">
         <v>14</v>
       </c>
       <c r="C47" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D47" s="24" t="s">
         <v>31</v>
@@ -8231,21 +8307,21 @@
         <v>4</v>
       </c>
       <c r="G47" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B48" s="24" t="s">
         <v>14</v>
       </c>
       <c r="C48" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D48" s="24" t="s">
         <v>35</v>
@@ -8257,25 +8333,25 @@
         <v>4</v>
       </c>
       <c r="G48" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="B49" s="24" t="s">
+      <c r="C49" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D49" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="C49" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="D49" s="24" t="s">
-        <v>129</v>
-      </c>
       <c r="E49" s="24">
         <v>3</v>
       </c>
@@ -8283,24 +8359,24 @@
         <v>3</v>
       </c>
       <c r="G49" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="24" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C50" s="24" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D50" s="24" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E50" s="24">
         <v>3</v>
@@ -8309,36 +8385,62 @@
         <v>3</v>
       </c>
       <c r="G50" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B51" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D51" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="C51" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="D51" s="24" t="s">
+      <c r="E51" s="24">
+        <v>3</v>
+      </c>
+      <c r="F51" s="24">
+        <v>3</v>
+      </c>
+      <c r="G51" s="24" t="s">
+        <v>434</v>
+      </c>
+      <c r="H51" s="24" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="E51" s="24">
-        <v>3</v>
-      </c>
-      <c r="F51" s="24">
-        <v>3</v>
-      </c>
-      <c r="G51" s="24" t="s">
-        <v>431</v>
-      </c>
-      <c r="H51" s="24" t="s">
-        <v>432</v>
+      <c r="B52" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D52" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E52" s="24">
+        <v>3</v>
+      </c>
+      <c r="F52" s="24">
+        <v>3</v>
+      </c>
+      <c r="G52" s="24" t="s">
+        <v>434</v>
+      </c>
+      <c r="H52" s="24" t="s">
+        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -8354,7 +8456,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="10" width="55" customWidth="1"/>
@@ -8362,7 +8464,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -8376,7 +8478,7 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
@@ -8393,7 +8495,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C4" s="32" t="s">
         <v>4</v>
@@ -8405,19 +8507,19 @@
         <v>7</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="J4" s="32" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -8437,19 +8539,19 @@
         <v>14</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -8469,19 +8571,19 @@
         <v>14</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="H6" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="J6" s="12" t="s">
         <v>448</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>449</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -8501,19 +8603,19 @@
         <v>14</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -8533,19 +8635,19 @@
         <v>14</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -8565,19 +8667,19 @@
         <v>14</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -8597,19 +8699,19 @@
         <v>14</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -8629,19 +8731,19 @@
         <v>14</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -8661,19 +8763,19 @@
         <v>14</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -8693,19 +8795,19 @@
         <v>14</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -8725,19 +8827,19 @@
         <v>14</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -8757,24 +8859,24 @@
         <v>14</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>14</v>
@@ -8789,24 +8891,24 @@
         <v>14</v>
       </c>
       <c r="F16" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="G16" s="34" t="s">
+        <v>445</v>
+      </c>
+      <c r="H16" s="12" t="s">
         <v>475</v>
       </c>
-      <c r="G16" s="34" t="s">
-        <v>442</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>476</v>
-      </c>
       <c r="I16" s="12" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>14</v>
@@ -8821,24 +8923,24 @@
         <v>14</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>14</v>
@@ -8853,24 +8955,24 @@
         <v>14</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>14</v>
@@ -8885,30 +8987,30 @@
         <v>14</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>464</v>
+        <v>445</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>460</v>
+        <v>484</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>70</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>71</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>17</v>
@@ -8917,30 +9019,30 @@
         <v>14</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="H20" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="I20" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="I20" s="12" t="s">
-        <v>444</v>
-      </c>
       <c r="J20" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>14</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>23</v>
@@ -8949,30 +9051,30 @@
         <v>14</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G21" s="33" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>27</v>
@@ -8981,30 +9083,30 @@
         <v>14</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>31</v>
@@ -9013,19 +9115,19 @@
         <v>14</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G23" s="33" t="s">
-        <v>459</v>
+        <v>489</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -9036,7 +9138,7 @@
         <v>14</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>35</v>
@@ -9045,19 +9147,19 @@
         <v>14</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -9077,19 +9179,19 @@
         <v>14</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G25" s="33" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -9109,19 +9211,19 @@
         <v>14</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G26" s="34" t="s">
-        <v>459</v>
+        <v>489</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -9141,19 +9243,19 @@
         <v>14</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="G27" s="33" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>464</v>
+        <v>495</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -9173,24 +9275,24 @@
         <v>14</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G28" s="34" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B29" s="13" t="s">
         <v>14</v>
@@ -9205,30 +9307,30 @@
         <v>14</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="G29" s="33" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="H29" s="14" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>99</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>17</v>
@@ -9237,30 +9339,30 @@
         <v>14</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G30" s="34" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>463</v>
+        <v>480</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B31" s="13" t="s">
         <v>14</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>23</v>
@@ -9269,30 +9371,30 @@
         <v>14</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G31" s="33" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="H31" s="14" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>27</v>
@@ -9301,30 +9403,30 @@
         <v>14</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="G32" s="34" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B33" s="13" t="s">
         <v>14</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>31</v>
@@ -9333,30 +9435,30 @@
         <v>14</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G33" s="33" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="H33" s="14" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>35</v>
@@ -9365,30 +9467,30 @@
         <v>14</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="G34" s="34" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>459</v>
+        <v>489</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="13" t="s">
         <v>113</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>114</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>17</v>
@@ -9397,30 +9499,30 @@
         <v>14</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="G35" s="33" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="H35" s="14" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>452</v>
+        <v>493</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>23</v>
@@ -9429,30 +9531,30 @@
         <v>14</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="G36" s="34" t="s">
+        <v>450</v>
+      </c>
+      <c r="H36" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="H36" s="12" t="s">
-        <v>444</v>
-      </c>
       <c r="I36" s="12" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B37" s="13" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>27</v>
@@ -9461,30 +9563,30 @@
         <v>14</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="G37" s="33" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="H37" s="14" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>31</v>
@@ -9493,30 +9595,30 @@
         <v>14</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G38" s="34" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B39" s="13" t="s">
         <v>14</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>35</v>
@@ -9525,115 +9627,147 @@
         <v>14</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="G39" s="33" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="H39" s="14" t="s">
-        <v>444</v>
+        <v>466</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>469</v>
+        <v>447</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="C40" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D40" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="C40" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="D40" s="11" t="s">
+      <c r="E40" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="E40" s="12" t="s">
-        <v>130</v>
-      </c>
       <c r="F40" s="12" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="G40" s="34" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E41" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="B41" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>135</v>
-      </c>
       <c r="F41" s="14" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="G41" s="33" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="H41" s="14" t="s">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="I41" s="14" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="J41" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B42" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D42" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="C42" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D42" s="11" t="s">
+      <c r="E42" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="G42" s="34" t="s">
+        <v>462</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="J42" s="12" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="E42" s="12" t="s">
+      <c r="B43" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D43" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="F42" s="12" t="s">
-        <v>511</v>
-      </c>
-      <c r="G42" s="34" t="s">
-        <v>478</v>
-      </c>
-      <c r="H42" s="12" t="s">
-        <v>463</v>
-      </c>
-      <c r="I42" s="12" t="s">
-        <v>444</v>
-      </c>
-      <c r="J42" s="12" t="s">
-        <v>445</v>
+      <c r="E43" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>514</v>
+      </c>
+      <c r="G43" s="33" t="s">
+        <v>466</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>472</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>493</v>
+      </c>
+      <c r="J43" s="14" t="s">
+        <v>448</v>
       </c>
     </row>
   </sheetData>
